--- a/mapeamento_layouts.xlsx
+++ b/mapeamento_layouts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2518"/>
+  <dimension ref="A1:C2525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37908,6 +37908,107 @@
         </is>
       </c>
     </row>
+    <row r="2519">
+      <c r="A2519" t="n">
+        <v>6454</v>
+      </c>
+      <c r="B2519" t="inlineStr">
+        <is>
+          <t>CONNECTERE - RELATÓRIO CONAS FINANCEIRAS</t>
+        </is>
+      </c>
+      <c r="C2519" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B2520" t="inlineStr">
+        <is>
+          <t>TRIBANCO 10033696 PDF INTERNET BANKING - JOTAPE</t>
+        </is>
+      </c>
+      <c r="C2520" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B2521" t="inlineStr">
+        <is>
+          <t>TRIBANCO 10033688 PDF INTERNET BANKING - JOTAPE</t>
+        </is>
+      </c>
+      <c r="C2521" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B2522" t="inlineStr">
+        <is>
+          <t>TRIBANCO 10035320 PDF INTERNET BANKING - JOTAPE FILIAL</t>
+        </is>
+      </c>
+      <c r="C2522" t="inlineStr"/>
+    </row>
+    <row r="2523">
+      <c r="A2523" t="n">
+        <v>6455</v>
+      </c>
+      <c r="B2523" t="inlineStr">
+        <is>
+          <t>WISE RH - RESUMO DA FOLHA DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2523" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" t="n">
+        <v>6456</v>
+      </c>
+      <c r="B2524" t="inlineStr">
+        <is>
+          <t>REAL CLUB - EXTRATO DA CONTA</t>
+        </is>
+      </c>
+      <c r="C2524" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B2525" t="inlineStr">
+        <is>
+          <t>OFX CAIXA MUNDIAL INDUSTRIA E COMERCIO DE URNAS LTDA</t>
+        </is>
+      </c>
+      <c r="C2525" t="inlineStr">
+        <is>
+          <t>OFX</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/mapeamento_layouts.xlsx
+++ b/mapeamento_layouts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2526"/>
+  <dimension ref="A1:C2667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>SAFRA - COMPROVANTE DE PAGAMENTO</t>
+          <t>SAFRA - COMPROVANTE DE PAGAMENTO DETRAN</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="B1461" t="inlineStr">
         <is>
-          <t>ATF BANK - EXTRATO</t>
+          <t>PAGME- EXTRATO</t>
         </is>
       </c>
       <c r="C1461" t="inlineStr">
@@ -31883,7 +31883,11 @@
           <t>MERCADO PAGO  - FATURA DE CARTÃO</t>
         </is>
       </c>
-      <c r="C2109" t="inlineStr"/>
+      <c r="C2109" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2110">
       <c r="A2110" t="n">
@@ -34709,7 +34713,11 @@
           <t>PROTON - LISTAGEM CRONOLOGICA DE TITULOS A PAGAR</t>
         </is>
       </c>
-      <c r="C2299" t="inlineStr"/>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2300">
       <c r="A2300" t="n">
@@ -34720,7 +34728,11 @@
           <t>SAID - DUPLICATAS LIQUIDADAS</t>
         </is>
       </c>
-      <c r="C2300" t="inlineStr"/>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2301">
       <c r="A2301" t="n">
@@ -36348,7 +36360,11 @@
           <t>SPDATA - CONTROLE DE ESTOQUE - MOVIMENTO POR CDC</t>
         </is>
       </c>
-      <c r="C2412" t="inlineStr"/>
+      <c r="C2412" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2413">
       <c r="A2413" t="n">
@@ -37775,7 +37791,11 @@
           <t>SICREDI - FATURA DE CARTÃO V2</t>
         </is>
       </c>
-      <c r="C2509" t="inlineStr"/>
+      <c r="C2509" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2510">
       <c r="A2510" t="n">
@@ -37786,7 +37806,11 @@
           <t>EFÍ BANK - EXTRATO FINANCEIRO</t>
         </is>
       </c>
-      <c r="C2510" t="inlineStr"/>
+      <c r="C2510" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2511">
       <c r="A2511" t="n">
@@ -37962,7 +37986,11 @@
           <t>TRIBANCO 10035320 PDF INTERNET BANKING - JOTAPE FILIAL</t>
         </is>
       </c>
-      <c r="C2522" t="inlineStr"/>
+      <c r="C2522" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="2523">
       <c r="A2523" t="n">
@@ -38019,6 +38047,2081 @@
         </is>
       </c>
       <c r="C2526" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" t="n">
+        <v>6458</v>
+      </c>
+      <c r="B2527" t="inlineStr">
+        <is>
+          <t>DOMÍNIO SERVIÇOS DIGITAIS - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2527" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="n">
+        <v>6459</v>
+      </c>
+      <c r="B2528" t="inlineStr">
+        <is>
+          <t>IDEALSOFT - CONTAS PAGAS POR FORNECEDOR</t>
+        </is>
+      </c>
+      <c r="C2528" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="n">
+        <v>1346</v>
+      </c>
+      <c r="B2529" t="inlineStr">
+        <is>
+          <t>SANTANDER - EXTRATO CONSOLIDADO METROPOLITAN</t>
+        </is>
+      </c>
+      <c r="C2529" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" t="n">
+        <v>6460</v>
+      </c>
+      <c r="B2530" t="inlineStr">
+        <is>
+          <t>SANTANDER - APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="C2530" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="n">
+        <v>6461</v>
+      </c>
+      <c r="B2531" t="inlineStr">
+        <is>
+          <t>MUBY - EXTRATO BANCARIO</t>
+        </is>
+      </c>
+      <c r="C2531" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" t="n">
+        <v>6462</v>
+      </c>
+      <c r="B2532" t="inlineStr">
+        <is>
+          <t>CONTMATIC - LANÇAMENTOS CONTA CORRENTE</t>
+        </is>
+      </c>
+      <c r="C2532" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" t="n">
+        <v>6463</v>
+      </c>
+      <c r="B2533" t="inlineStr">
+        <is>
+          <t>ALTERDATA - RELATÓRIO DE CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2533" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" t="n">
+        <v>6464</v>
+      </c>
+      <c r="B2534" t="inlineStr">
+        <is>
+          <t>ALTERDATA - LANÇAMENTOS FINANCEIROS CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2534" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B2535" t="inlineStr">
+        <is>
+          <t>PREFEITURA DE MOGI DAS CRUZES - NFE LISTAGEM</t>
+        </is>
+      </c>
+      <c r="C2535" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" t="n">
+        <v>6466</v>
+      </c>
+      <c r="B2536" t="inlineStr">
+        <is>
+          <t>ALTERDATA - RELATÓRIO DE CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2536" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="n">
+        <v>6467</v>
+      </c>
+      <c r="B2537" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - RELATÓRIO DE VENDAS</t>
+        </is>
+      </c>
+      <c r="C2537" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" t="n">
+        <v>6468</v>
+      </c>
+      <c r="B2538" t="inlineStr">
+        <is>
+          <t>SIACON - RELAÇÃO DE BOLETOS BAIXADOS</t>
+        </is>
+      </c>
+      <c r="C2538" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B2539" t="inlineStr">
+        <is>
+          <t>JOELMA PIMENTA - CONTA GARANTIDA JP</t>
+        </is>
+      </c>
+      <c r="C2539" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" t="n">
+        <v>6469</v>
+      </c>
+      <c r="B2540" t="inlineStr">
+        <is>
+          <t>BANCO WISE - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2540" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" t="n">
+        <v>6470</v>
+      </c>
+      <c r="B2541" t="inlineStr">
+        <is>
+          <t>GC WEB - RELATÓRIO DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2541" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" t="n">
+        <v>6471</v>
+      </c>
+      <c r="B2542" t="inlineStr">
+        <is>
+          <t>SICREDI - FATURA CARTÃO DE CRÉDITO</t>
+        </is>
+      </c>
+      <c r="C2542" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B2543" t="inlineStr">
+        <is>
+          <t>CEF - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2543" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" t="n">
+        <v>6473</v>
+      </c>
+      <c r="B2544" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - EXTRATO TXT V2</t>
+        </is>
+      </c>
+      <c r="C2544" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B2545" t="inlineStr">
+        <is>
+          <t>MEGAFLEX - GESTÃO FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="C2545" t="inlineStr"/>
+    </row>
+    <row r="2546">
+      <c r="A2546" t="n">
+        <v>6475</v>
+      </c>
+      <c r="B2546" t="inlineStr">
+        <is>
+          <t>BANCO SEMEAR - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2546" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B2547" t="inlineStr">
+        <is>
+          <t>ITAU - HC COMERCIO CC 32701</t>
+        </is>
+      </c>
+      <c r="C2547" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" t="n">
+        <v>6476</v>
+      </c>
+      <c r="B2548" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - DESPESAS</t>
+        </is>
+      </c>
+      <c r="C2548" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" t="n">
+        <v>6477</v>
+      </c>
+      <c r="B2549" t="inlineStr">
+        <is>
+          <t>LINX SISTEMAS - RAZÃO CONTÁBIL</t>
+        </is>
+      </c>
+      <c r="C2549" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" t="n">
+        <v>6478</v>
+      </c>
+      <c r="B2550" t="inlineStr">
+        <is>
+          <t>SISGEN - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2550" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" t="n">
+        <v>6479</v>
+      </c>
+      <c r="B2551" t="inlineStr">
+        <is>
+          <t>SISGEN - CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2551" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" t="n">
+        <v>6480</v>
+      </c>
+      <c r="B2552" t="inlineStr">
+        <is>
+          <t>EASY CONTROL - TITULOS RECEBIDOS</t>
+        </is>
+      </c>
+      <c r="C2552" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" t="n">
+        <v>6481</v>
+      </c>
+      <c r="B2553" t="inlineStr">
+        <is>
+          <t>OTTIMIZZA - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2553" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" t="n">
+        <v>6482</v>
+      </c>
+      <c r="B2554" t="inlineStr">
+        <is>
+          <t>SANKHYA - MOVIMENTAÇÃO DE TITULOS FINANCEIROS</t>
+        </is>
+      </c>
+      <c r="C2554" t="inlineStr"/>
+    </row>
+    <row r="2555">
+      <c r="A2555" t="n">
+        <v>6483</v>
+      </c>
+      <c r="B2555" t="inlineStr">
+        <is>
+          <t>UBS - ACCOUNT TRANSACTIONS</t>
+        </is>
+      </c>
+      <c r="C2555" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" t="n">
+        <v>6484</v>
+      </c>
+      <c r="B2556" t="inlineStr">
+        <is>
+          <t>BTG PACTUAL - DECLARAÇÃO (STATEMENT)</t>
+        </is>
+      </c>
+      <c r="C2556" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" t="n">
+        <v>6485</v>
+      </c>
+      <c r="B2557" t="inlineStr">
+        <is>
+          <t>INVEST BRAVO PAGME - DEMONSTRATIVO DE CESSÃO DE CRÉDITO</t>
+        </is>
+      </c>
+      <c r="C2557" t="inlineStr"/>
+    </row>
+    <row r="2558">
+      <c r="A2558" t="n">
+        <v>6486</v>
+      </c>
+      <c r="B2558" t="inlineStr">
+        <is>
+          <t>BTG/EQI - EXTRATO DA CONTA INVESTIMENTO</t>
+        </is>
+      </c>
+      <c r="C2558" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" t="n">
+        <v>6487</v>
+      </c>
+      <c r="B2559" t="inlineStr">
+        <is>
+          <t>TOTVS - VALORES DE FERIAS</t>
+        </is>
+      </c>
+      <c r="C2559" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" t="n">
+        <v>1265</v>
+      </c>
+      <c r="B2560" t="inlineStr">
+        <is>
+          <t>CONFRONTO NUBANK</t>
+        </is>
+      </c>
+      <c r="C2560" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" t="n">
+        <v>6488</v>
+      </c>
+      <c r="B2561" t="inlineStr">
+        <is>
+          <t>INVEST BRAVO - PROPOSTA DE AQUISIÇÃO DE CRÉDITO</t>
+        </is>
+      </c>
+      <c r="C2561" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" t="n">
+        <v>6489</v>
+      </c>
+      <c r="B2562" t="inlineStr">
+        <is>
+          <t>SICOOB - RELATORIO DE LANÇAMENTO EM CONTA - SINTÉTICO</t>
+        </is>
+      </c>
+      <c r="C2562" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" t="n">
+        <v>6490</v>
+      </c>
+      <c r="B2563" t="inlineStr">
+        <is>
+          <t>COMPROVANTES - NFSE V2</t>
+        </is>
+      </c>
+      <c r="C2563" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" t="n">
+        <v>6491</v>
+      </c>
+      <c r="B2564" t="inlineStr">
+        <is>
+          <t>VISUAL SUL - PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2564" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" t="n">
+        <v>6492</v>
+      </c>
+      <c r="B2565" t="inlineStr">
+        <is>
+          <t>EASY CONTROL - EXTRATO DA CONTA</t>
+        </is>
+      </c>
+      <c r="C2565" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" t="n">
+        <v>6493</v>
+      </c>
+      <c r="B2566" t="inlineStr">
+        <is>
+          <t>BTG PACTUAL - FATURA DE CARTÃO</t>
+        </is>
+      </c>
+      <c r="C2566" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" t="n">
+        <v>6494</v>
+      </c>
+      <c r="B2567" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - RELATÓRIO DETALHADO DE ENTRADAS</t>
+        </is>
+      </c>
+      <c r="C2567" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" t="n">
+        <v>6495</v>
+      </c>
+      <c r="B2568" t="inlineStr">
+        <is>
+          <t>FDC - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2568" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" t="n">
+        <v>6496</v>
+      </c>
+      <c r="B2569" t="inlineStr">
+        <is>
+          <t>INVEST BRAVO PAGME - BORDERÔ</t>
+        </is>
+      </c>
+      <c r="C2569" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" t="n">
+        <v>6497</v>
+      </c>
+      <c r="B2570" t="inlineStr">
+        <is>
+          <t>SOFTPLAN - EXTRATO CREDOR (PERSONALIZADO)</t>
+        </is>
+      </c>
+      <c r="C2570" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" t="n">
+        <v>6498</v>
+      </c>
+      <c r="B2571" t="inlineStr">
+        <is>
+          <t>APRESENTA.ME - CONTAS A PAGAR E RECEBER</t>
+        </is>
+      </c>
+      <c r="C2571" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" t="n">
+        <v>6499</v>
+      </c>
+      <c r="B2572" t="inlineStr">
+        <is>
+          <t>DOMÍNIO - PREVISÃO</t>
+        </is>
+      </c>
+      <c r="C2572" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" t="n">
+        <v>6500</v>
+      </c>
+      <c r="B2573" t="inlineStr">
+        <is>
+          <t>GROUP SOFTWARE - FLUXO DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2573" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" t="n">
+        <v>6501</v>
+      </c>
+      <c r="B2574" t="inlineStr">
+        <is>
+          <t>SKYTINS DATA - FLUXO DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2574" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" t="n">
+        <v>6502</v>
+      </c>
+      <c r="B2575" t="inlineStr">
+        <is>
+          <t>SKYTINS DATA - TITULOS A PAGAR BAIXADOS</t>
+        </is>
+      </c>
+      <c r="C2575" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B2576" t="inlineStr">
+        <is>
+          <t>ITAU EMPRESAS 99609-0</t>
+        </is>
+      </c>
+      <c r="C2576" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" t="n">
+        <v>6503</v>
+      </c>
+      <c r="B2577" t="inlineStr">
+        <is>
+          <t>BB - FOLHA DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2577" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" t="n">
+        <v>6504</v>
+      </c>
+      <c r="B2578" t="inlineStr">
+        <is>
+          <t>360 ERP - TITULOS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2578" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" t="n">
+        <v>6505</v>
+      </c>
+      <c r="B2579" t="inlineStr">
+        <is>
+          <t>ITAU - MOVIMENTAÇÃO RESUMIDA DE COBRANÇA (TODOS OS TIPOS)</t>
+        </is>
+      </c>
+      <c r="C2579" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" t="n">
+        <v>6506</v>
+      </c>
+      <c r="B2580" t="inlineStr">
+        <is>
+          <t>SUPERLOGICA - DESPESAS V2</t>
+        </is>
+      </c>
+      <c r="C2580" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" t="n">
+        <v>6507</v>
+      </c>
+      <c r="B2581" t="inlineStr">
+        <is>
+          <t>SOFTPLAN - EXTRATO CREDOR</t>
+        </is>
+      </c>
+      <c r="C2581" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" t="n">
+        <v>6508</v>
+      </c>
+      <c r="B2582" t="inlineStr">
+        <is>
+          <t>CONTROLE FINANCEIRO - CONCILIAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2582" t="inlineStr">
+        <is>
+          <t>TEXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" t="n">
+        <v>6509</v>
+      </c>
+      <c r="B2583" t="inlineStr">
+        <is>
+          <t>SICOOB - RELATÓRIO DE PAGAMENTOS V3</t>
+        </is>
+      </c>
+      <c r="C2583" t="inlineStr"/>
+    </row>
+    <row r="2584">
+      <c r="A2584" t="n">
+        <v>6510</v>
+      </c>
+      <c r="B2584" t="inlineStr">
+        <is>
+          <t>ITAU - DECLARAÇÃO (STATEMENT)</t>
+        </is>
+      </c>
+      <c r="C2584" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" t="n">
+        <v>6511</v>
+      </c>
+      <c r="B2585" t="inlineStr">
+        <is>
+          <t>UBS - EXTRACT OF ACCOUNT</t>
+        </is>
+      </c>
+      <c r="C2585" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" t="n">
+        <v>6512</v>
+      </c>
+      <c r="B2586" t="inlineStr">
+        <is>
+          <t>SENSATTA - RELAÇÃO DE DEPRECIAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2586" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" t="n">
+        <v>6513</v>
+      </c>
+      <c r="B2587" t="inlineStr">
+        <is>
+          <t>ECO CENTAURO - DOCUMENTOS RECEBIDOS POR PORTADOR</t>
+        </is>
+      </c>
+      <c r="C2587" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" t="n">
+        <v>6514</v>
+      </c>
+      <c r="B2588" t="inlineStr">
+        <is>
+          <t>IMPOSTOS ESTADUAIS - GNRE</t>
+        </is>
+      </c>
+      <c r="C2588" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" t="n">
+        <v>6515</v>
+      </c>
+      <c r="B2589" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - FLUXO DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2589" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" t="n">
+        <v>6516</v>
+      </c>
+      <c r="B2590" t="inlineStr">
+        <is>
+          <t>360 ERP - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2590" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B2591" t="inlineStr">
+        <is>
+          <t>RELATÓRIO PAGAMENTOS ARPA CRESOL</t>
+        </is>
+      </c>
+      <c r="C2591" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" t="n">
+        <v>6517</v>
+      </c>
+      <c r="B2592" t="inlineStr">
+        <is>
+          <t>TECNOVIX - EXTRATO BANCARIO</t>
+        </is>
+      </c>
+      <c r="C2592" t="inlineStr"/>
+    </row>
+    <row r="2593">
+      <c r="A2593" t="n">
+        <v>6518</v>
+      </c>
+      <c r="B2593" t="inlineStr">
+        <is>
+          <t>TOTVS - FOLHA E ADIANTAMENTO</t>
+        </is>
+      </c>
+      <c r="C2593" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2594">
+      <c r="A2594" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B2594" t="inlineStr">
+        <is>
+          <t>SISLOC - CARTAO DE CREDITO SICOOB</t>
+        </is>
+      </c>
+      <c r="C2594" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" t="n">
+        <v>6519</v>
+      </c>
+      <c r="B2595" t="inlineStr">
+        <is>
+          <t>TOTVS - VALORES RESCISÃO</t>
+        </is>
+      </c>
+      <c r="C2595" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" t="n">
+        <v>6520</v>
+      </c>
+      <c r="B2596" t="inlineStr">
+        <is>
+          <t>DOMÍNIO - RESUMO DA FOLHA V3</t>
+        </is>
+      </c>
+      <c r="C2596" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" t="n">
+        <v>1245</v>
+      </c>
+      <c r="B2597" t="inlineStr">
+        <is>
+          <t>CONFRONTO SANTANDER</t>
+        </is>
+      </c>
+      <c r="C2597" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" t="n">
+        <v>6521</v>
+      </c>
+      <c r="B2598" t="inlineStr">
+        <is>
+          <t>ORIGEM - CONTAS RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C2598" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" t="n">
+        <v>6522</v>
+      </c>
+      <c r="B2599" t="inlineStr">
+        <is>
+          <t>AGILLI - EXTRATO CONVENIADA</t>
+        </is>
+      </c>
+      <c r="C2599" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" t="n">
+        <v>6523</v>
+      </c>
+      <c r="B2600" t="inlineStr">
+        <is>
+          <t>CIELO - TOTAL DE TAXAS POR DIA</t>
+        </is>
+      </c>
+      <c r="C2600" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" t="n">
+        <v>6524</v>
+      </c>
+      <c r="B2601" t="inlineStr">
+        <is>
+          <t>CLOUD COMMERCE - GERENCIADOR FINANCEIRO NOTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2601" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" t="n">
+        <v>6525</v>
+      </c>
+      <c r="B2602" t="inlineStr">
+        <is>
+          <t>PCNET - CONTAS PAGAS</t>
+        </is>
+      </c>
+      <c r="C2602" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" t="n">
+        <v>6526</v>
+      </c>
+      <c r="B2603" t="inlineStr">
+        <is>
+          <t>ARTIZ - RELATÓRIO DE DESPESAS</t>
+        </is>
+      </c>
+      <c r="C2603" t="inlineStr"/>
+    </row>
+    <row r="2604">
+      <c r="A2604" t="n">
+        <v>6527</v>
+      </c>
+      <c r="B2604" t="inlineStr">
+        <is>
+          <t>INFARMA - CONTAS PAGAS POR EMISSÃO/VENCIMENTO V2</t>
+        </is>
+      </c>
+      <c r="C2604" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" t="n">
+        <v>6528</v>
+      </c>
+      <c r="B2605" t="inlineStr">
+        <is>
+          <t>LEVE CARGAS - RELATÓRIO DE PAGAMENTO IMPOSTOS RETIDOS</t>
+        </is>
+      </c>
+      <c r="C2605" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" t="n">
+        <v>6529</v>
+      </c>
+      <c r="B2606" t="inlineStr">
+        <is>
+          <t>LEVE CARGAS - RELATÓRIO DE CARTAS FRETE</t>
+        </is>
+      </c>
+      <c r="C2606" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" t="n">
+        <v>6530</v>
+      </c>
+      <c r="B2607" t="inlineStr">
+        <is>
+          <t>BANKEL - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2607" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" t="n">
+        <v>6531</v>
+      </c>
+      <c r="B2608" t="inlineStr">
+        <is>
+          <t>SIAGRI - CONTAS PAGAS FORNECEDOR</t>
+        </is>
+      </c>
+      <c r="C2608" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" t="n">
+        <v>6532</v>
+      </c>
+      <c r="B2609" t="inlineStr">
+        <is>
+          <t>MULVI PAY - MOVIMENTAÇÃO DE VENDAS</t>
+        </is>
+      </c>
+      <c r="C2609" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" t="n">
+        <v>6533</v>
+      </c>
+      <c r="B2610" t="inlineStr">
+        <is>
+          <t>BRAJAN - RELAÇÃO DE PAGAMENTOS AGRUPADA POR DATA DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2610" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" t="n">
+        <v>6534</v>
+      </c>
+      <c r="B2611" t="inlineStr">
+        <is>
+          <t>GETNET - VALORES REALIZADOS E FUTUROS</t>
+        </is>
+      </c>
+      <c r="C2611" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" t="n">
+        <v>6535</v>
+      </c>
+      <c r="B2612" t="inlineStr">
+        <is>
+          <t>BANCO ID - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2612" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" t="n">
+        <v>6536</v>
+      </c>
+      <c r="B2613" t="inlineStr">
+        <is>
+          <t>LEVE CARGAS - MOVIMENTAÇÃO BANCÁRIA</t>
+        </is>
+      </c>
+      <c r="C2613" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" t="n">
+        <v>6537</v>
+      </c>
+      <c r="B2614" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2614" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" t="n">
+        <v>6538</v>
+      </c>
+      <c r="B2615" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - DEMONSTRATIVO DAS DESPESAS</t>
+        </is>
+      </c>
+      <c r="C2615" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" t="n">
+        <v>1268</v>
+      </c>
+      <c r="B2616" t="inlineStr">
+        <is>
+          <t>BGE - APLICAÇÃO DIÁRIA Nº 29</t>
+        </is>
+      </c>
+      <c r="C2616" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" t="n">
+        <v>6539</v>
+      </c>
+      <c r="B2617" t="inlineStr">
+        <is>
+          <t>BANCO ID - COMPROVANTES DE PAGAMENTO/RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="C2617" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" t="n">
+        <v>6540</v>
+      </c>
+      <c r="B2618" t="inlineStr">
+        <is>
+          <t>W3ERP - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2618" t="inlineStr"/>
+    </row>
+    <row r="2619">
+      <c r="A2619" t="n">
+        <v>6541</v>
+      </c>
+      <c r="B2619" t="inlineStr">
+        <is>
+          <t>PAGBANK  - FATURA DE CARTÃO</t>
+        </is>
+      </c>
+      <c r="C2619" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" t="n">
+        <v>6542</v>
+      </c>
+      <c r="B2620" t="inlineStr">
+        <is>
+          <t>AUTOMATIZA - CONTAS PAGAR</t>
+        </is>
+      </c>
+      <c r="C2620" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" t="n">
+        <v>6543</v>
+      </c>
+      <c r="B2621" t="inlineStr">
+        <is>
+          <t>SIGEM - FLUXO CAIXA</t>
+        </is>
+      </c>
+      <c r="C2621" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" t="n">
+        <v>6544</v>
+      </c>
+      <c r="B2622" t="inlineStr">
+        <is>
+          <t>IXCSOFT - CONTAS A PAGAR ANALITICO</t>
+        </is>
+      </c>
+      <c r="C2622" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" t="n">
+        <v>1341</v>
+      </c>
+      <c r="B2623" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 387743 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2623" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" t="n">
+        <v>1343</v>
+      </c>
+      <c r="B2624" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 387662 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2624" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" t="n">
+        <v>1332</v>
+      </c>
+      <c r="B2625" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 389312 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2625" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" t="n">
+        <v>1333</v>
+      </c>
+      <c r="B2626" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 389134 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2626" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" t="n">
+        <v>1334</v>
+      </c>
+      <c r="B2627" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 387700- PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2627" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" t="n">
+        <v>6545</v>
+      </c>
+      <c r="B2628" t="inlineStr">
+        <is>
+          <t>AVANTE FOOD - RELATÓRIO DE MOVIMENTAÇÃO DIÁRIA</t>
+        </is>
+      </c>
+      <c r="C2628" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" t="n">
+        <v>6546</v>
+      </c>
+      <c r="B2629" t="inlineStr">
+        <is>
+          <t>SISTEMA DESCONHECIDO - RELATÓRIO DE CAIXA ATUAL</t>
+        </is>
+      </c>
+      <c r="C2629" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" t="n">
+        <v>6547</v>
+      </c>
+      <c r="B2630" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2630" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" t="n">
+        <v>6548</v>
+      </c>
+      <c r="B2631" t="inlineStr">
+        <is>
+          <t>QUESTOR - REGISTRO DE SAIDAS</t>
+        </is>
+      </c>
+      <c r="C2631" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" t="n">
+        <v>6549</v>
+      </c>
+      <c r="B2632" t="inlineStr">
+        <is>
+          <t>PORTAL SOFT - TITULOS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2632" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" t="n">
+        <v>6550</v>
+      </c>
+      <c r="B2633" t="inlineStr">
+        <is>
+          <t>AMSOFT - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2633" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" t="n">
+        <v>6551</v>
+      </c>
+      <c r="B2634" t="inlineStr">
+        <is>
+          <t>SAFRA - COMPROVANTES DE PAGAMENTO V2</t>
+        </is>
+      </c>
+      <c r="C2634" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B2635" t="inlineStr">
+        <is>
+          <t>CLOUD COMMERCE - GERENCIADOR FINANCEIRO V2</t>
+        </is>
+      </c>
+      <c r="C2635" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" t="n">
+        <v>1951</v>
+      </c>
+      <c r="B2636" t="inlineStr">
+        <is>
+          <t>VISTO SISTEMAS - APLICAÇÃO SANTANDER PDF</t>
+        </is>
+      </c>
+      <c r="C2636" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" t="n">
+        <v>2289</v>
+      </c>
+      <c r="B2637" t="inlineStr">
+        <is>
+          <t>APLICAÇÃO CEF - ORTOS SOROCABA -</t>
+        </is>
+      </c>
+      <c r="C2637" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B2638" t="inlineStr">
+        <is>
+          <t>ALELO - EXTRATO CARTÃO</t>
+        </is>
+      </c>
+      <c r="C2638" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" t="n">
+        <v>6554</v>
+      </c>
+      <c r="B2639" t="inlineStr">
+        <is>
+          <t>UAU! SOFTWARE - CONTAS RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C2639" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" t="n">
+        <v>6555</v>
+      </c>
+      <c r="B2640" t="inlineStr">
+        <is>
+          <t>TELLACE SISTEMAS - RELATÓRIO CONCILIAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2640" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" t="n">
+        <v>6556</v>
+      </c>
+      <c r="B2641" t="inlineStr">
+        <is>
+          <t>RED - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2641" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" t="n">
+        <v>6557</v>
+      </c>
+      <c r="B2642" t="inlineStr">
+        <is>
+          <t>LUSO BRASILEIRO - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2642" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" t="n">
+        <v>6558</v>
+      </c>
+      <c r="B2643" t="inlineStr">
+        <is>
+          <t>SICOOB - EXTRATO SICOOB V3</t>
+        </is>
+      </c>
+      <c r="C2643" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" t="n">
+        <v>6559</v>
+      </c>
+      <c r="B2644" t="inlineStr">
+        <is>
+          <t>DANTEC - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2644" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" t="n">
+        <v>6560</v>
+      </c>
+      <c r="B2645" t="inlineStr">
+        <is>
+          <t>ZENITE - CONTAS PAGAS POR DATA</t>
+        </is>
+      </c>
+      <c r="C2645" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" t="n">
+        <v>6561</v>
+      </c>
+      <c r="B2646" t="inlineStr">
+        <is>
+          <t>ALELO - EXTRATO CONTA EMPRESA</t>
+        </is>
+      </c>
+      <c r="C2646" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" t="n">
+        <v>6562</v>
+      </c>
+      <c r="B2647" t="inlineStr">
+        <is>
+          <t>BB - DEMONSTRATIVO DE CARTÃO PORTADOR</t>
+        </is>
+      </c>
+      <c r="C2647" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" t="n">
+        <v>6563</v>
+      </c>
+      <c r="B2648" t="inlineStr">
+        <is>
+          <t>PAYONEER - ACCOUNT STATEMENT</t>
+        </is>
+      </c>
+      <c r="C2648" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" t="n">
+        <v>1238</v>
+      </c>
+      <c r="B2649" t="inlineStr">
+        <is>
+          <t>COPESITA WB</t>
+        </is>
+      </c>
+      <c r="C2649" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B2650" t="inlineStr">
+        <is>
+          <t>537 - NUBANK GERALDA</t>
+        </is>
+      </c>
+      <c r="C2650" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" t="n">
+        <v>6564</v>
+      </c>
+      <c r="B2651" t="inlineStr">
+        <is>
+          <t>WINTHOR - TITULOS RECEBIDOS SINTÉTICO V1</t>
+        </is>
+      </c>
+      <c r="C2651" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" t="n">
+        <v>6565</v>
+      </c>
+      <c r="B2652" t="inlineStr">
+        <is>
+          <t>ACONTEC - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2652" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" t="n">
+        <v>6566</v>
+      </c>
+      <c r="B2653" t="inlineStr">
+        <is>
+          <t>SRK - RESUMO DE PAGAMENTOS A FORNECEDORES</t>
+        </is>
+      </c>
+      <c r="C2653" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" t="n">
+        <v>6567</v>
+      </c>
+      <c r="B2654" t="inlineStr">
+        <is>
+          <t>TOTVS - LANÇAMENTOS POR PROCESSOS CONTABEIS</t>
+        </is>
+      </c>
+      <c r="C2654" t="inlineStr"/>
+    </row>
+    <row r="2655">
+      <c r="A2655" t="n">
+        <v>6568</v>
+      </c>
+      <c r="B2655" t="inlineStr">
+        <is>
+          <t>CERTTUS - MOVIMENTO DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2655" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" t="n">
+        <v>6569</v>
+      </c>
+      <c r="B2656" t="inlineStr">
+        <is>
+          <t>QUINTO ANDAR - DEMONSTRATIVO FINANCEIRO DETALHADO</t>
+        </is>
+      </c>
+      <c r="C2656" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" t="n">
+        <v>6570</v>
+      </c>
+      <c r="B2657" t="inlineStr">
+        <is>
+          <t>BANCO SQUID - RECEBIVEIS BAIXADOS</t>
+        </is>
+      </c>
+      <c r="C2657" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B2658" t="inlineStr">
+        <is>
+          <t>CLINUX - EXTRATO BRADESCO</t>
+        </is>
+      </c>
+      <c r="C2658" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" t="n">
+        <v>6571</v>
+      </c>
+      <c r="B2659" t="inlineStr">
+        <is>
+          <t>SIGEM - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2659" t="inlineStr"/>
+    </row>
+    <row r="2660">
+      <c r="A2660" t="n">
+        <v>6572</v>
+      </c>
+      <c r="B2660" t="inlineStr">
+        <is>
+          <t>RAFFINATO - TÍTULOS À PAGAR</t>
+        </is>
+      </c>
+      <c r="C2660" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" t="n">
+        <v>6573</v>
+      </c>
+      <c r="B2661" t="inlineStr">
+        <is>
+          <t>DEGUST - RECEITA DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2661" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" t="n">
+        <v>6574</v>
+      </c>
+      <c r="B2662" t="inlineStr">
+        <is>
+          <t>FRONTSYS - EXTRATO DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2662" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B2663" t="inlineStr">
+        <is>
+          <t>CEF 144-0</t>
+        </is>
+      </c>
+      <c r="C2663" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" t="n">
+        <v>6575</v>
+      </c>
+      <c r="B2664" t="inlineStr">
+        <is>
+          <t>TOUCH - EXTRATO BANCARIO POR COMPENSAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2664" t="inlineStr"/>
+    </row>
+    <row r="2665">
+      <c r="A2665" t="n">
+        <v>6576</v>
+      </c>
+      <c r="B2665" t="inlineStr">
+        <is>
+          <t>FÁCIL SISTEMAS - EXTRATO DA CONTA</t>
+        </is>
+      </c>
+      <c r="C2665" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" t="n">
+        <v>6577</v>
+      </c>
+      <c r="B2666" t="inlineStr">
+        <is>
+          <t>SMART FATORING - RELATÓRIO DE TITULOS</t>
+        </is>
+      </c>
+      <c r="C2666" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" t="n">
+        <v>6578</v>
+      </c>
+      <c r="B2667" t="inlineStr">
+        <is>
+          <t>PREFEITURA MUNICIPAL DE SÃO SEBASTIÃO DO PARAÍSO -  IMPRESSÃO RESUMIDA</t>
+        </is>
+      </c>
+      <c r="C2667" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/mapeamento_layouts.xlsx
+++ b/mapeamento_layouts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2667"/>
+  <dimension ref="A1:C2808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>TXT</t>
         </is>
       </c>
     </row>
@@ -20323,7 +20323,7 @@
       </c>
       <c r="C1327" t="inlineStr">
         <is>
-          <t>PDF</t>
+          <t>TEXTO</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,11 @@
           <t>SPF BANK - EXTRATO</t>
         </is>
       </c>
-      <c r="C1472" t="inlineStr"/>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
     </row>
     <row r="1473">
       <c r="A1473" t="n">
@@ -34500,7 +34504,7 @@
       </c>
       <c r="B2285" t="inlineStr">
         <is>
-          <t>NFE - NFE</t>
+          <t>NFE - XML DE SAÍDA</t>
         </is>
       </c>
       <c r="C2285" t="inlineStr">
@@ -38033,7 +38037,7 @@
       </c>
       <c r="C2525" t="inlineStr">
         <is>
-          <t>OFX</t>
+          <t>PDF</t>
         </is>
       </c>
     </row>
@@ -40122,6 +40126,2069 @@
         </is>
       </c>
       <c r="C2667" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" t="n">
+        <v>6579</v>
+      </c>
+      <c r="B2668" t="inlineStr">
+        <is>
+          <t>EGS - CONTAS RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C2668" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" t="n">
+        <v>6580</v>
+      </c>
+      <c r="B2669" t="inlineStr">
+        <is>
+          <t>IDEALSOFT - RECEBIVEIS BAIXADOS (PERSONALIZADO)</t>
+        </is>
+      </c>
+      <c r="C2669" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" t="n">
+        <v>6581</v>
+      </c>
+      <c r="B2670" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - BOLETOS PAGOS TXT</t>
+        </is>
+      </c>
+      <c r="C2670" t="inlineStr">
+        <is>
+          <t>TXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" t="n">
+        <v>6582</v>
+      </c>
+      <c r="B2671" t="inlineStr">
+        <is>
+          <t>CAIXA ECONOMICA -  ESPELHO DE RETORNO</t>
+        </is>
+      </c>
+      <c r="C2671" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" t="n">
+        <v>6583</v>
+      </c>
+      <c r="B2672" t="inlineStr">
+        <is>
+          <t>WK RADAR -  ISS PROPRIO A RECOLHER</t>
+        </is>
+      </c>
+      <c r="C2672" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" t="n">
+        <v>6584</v>
+      </c>
+      <c r="B2673" t="inlineStr">
+        <is>
+          <t>EGS - CONTAS PAGAS</t>
+        </is>
+      </c>
+      <c r="C2673" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" t="n">
+        <v>6585</v>
+      </c>
+      <c r="B2674" t="inlineStr">
+        <is>
+          <t>SISTEMA PARA ADMINISTRAÇÃO DE TRANSPORTE -  EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2674" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" t="n">
+        <v>6586</v>
+      </c>
+      <c r="B2675" t="inlineStr">
+        <is>
+          <t>ITAÚ - EXTRATO DE FUNDOS DE INVESTIMENTOS</t>
+        </is>
+      </c>
+      <c r="C2675" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" t="n">
+        <v>6587</v>
+      </c>
+      <c r="B2676" t="inlineStr">
+        <is>
+          <t>BLING - RELATÓRIO DE NOTAS FISCAIS DE SAÍDA</t>
+        </is>
+      </c>
+      <c r="C2676" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="n">
+        <v>6588</v>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>SOFT TRADE - FOLHA DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" t="n">
+        <v>6589</v>
+      </c>
+      <c r="B2678" t="inlineStr">
+        <is>
+          <t>NFSE - NOTA FISCAL DE SERVIÇO XML V2</t>
+        </is>
+      </c>
+      <c r="C2678" t="inlineStr">
+        <is>
+          <t>XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" t="n">
+        <v>6590</v>
+      </c>
+      <c r="B2679" t="inlineStr">
+        <is>
+          <t>CEF - FATURA CARTÃO COM SENHA V2</t>
+        </is>
+      </c>
+      <c r="C2679" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" t="n">
+        <v>6591</v>
+      </c>
+      <c r="B2680" t="inlineStr">
+        <is>
+          <t>VENTURA INVEST - DEMONSTRATIVO DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="C2680" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" t="n">
+        <v>6592</v>
+      </c>
+      <c r="B2681" t="inlineStr">
+        <is>
+          <t>APPELFINANCE - BAIXA DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2681" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" t="n">
+        <v>6593</v>
+      </c>
+      <c r="B2682" t="inlineStr">
+        <is>
+          <t>SICOOB - COMPROVANTES DE RECEBIMENTO (BAIXADOS)</t>
+        </is>
+      </c>
+      <c r="C2682" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" t="n">
+        <v>6594</v>
+      </c>
+      <c r="B2683" t="inlineStr">
+        <is>
+          <t>SANTANDER - RESUMO DE OPERAÇÃO DE ANTECIPAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2683" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" t="n">
+        <v>6595</v>
+      </c>
+      <c r="B2684" t="inlineStr">
+        <is>
+          <t>SICREDI - CONTRATO DE CREDITO</t>
+        </is>
+      </c>
+      <c r="C2684" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" t="n">
+        <v>1316</v>
+      </c>
+      <c r="B2685" t="inlineStr">
+        <is>
+          <t>BRADESCO FILIAL PAMPULHA - 8</t>
+        </is>
+      </c>
+      <c r="C2685" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" t="n">
+        <v>6596</v>
+      </c>
+      <c r="B2686" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - PRE ESPELHO DA FATURA POR TITULAR</t>
+        </is>
+      </c>
+      <c r="C2686" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" t="n">
+        <v>6597</v>
+      </c>
+      <c r="B2687" t="inlineStr">
+        <is>
+          <t>SOFTPOOL - EXTRATO ANALÍTICO P/ SIMPLES CONFERÊNCIA</t>
+        </is>
+      </c>
+      <c r="C2687" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" t="n">
+        <v>6598</v>
+      </c>
+      <c r="B2688" t="inlineStr">
+        <is>
+          <t>PREF. BELO HORIZONTE - ISS RETIDO A RECOLHER</t>
+        </is>
+      </c>
+      <c r="C2688" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B2689" t="inlineStr">
+        <is>
+          <t>CARTÃO DE CRÉDITO - 9764</t>
+        </is>
+      </c>
+      <c r="C2689" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2690">
+      <c r="A2690" t="n">
+        <v>6599</v>
+      </c>
+      <c r="B2690" t="inlineStr">
+        <is>
+          <t>AMIGO PAY - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2690" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" t="n">
+        <v>6600</v>
+      </c>
+      <c r="B2691" t="inlineStr">
+        <is>
+          <t>WHINTOR - EXTRATO COMPENSAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2691" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" t="n">
+        <v>6601</v>
+      </c>
+      <c r="B2692" t="inlineStr">
+        <is>
+          <t>NOMUS - PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2692" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" t="n">
+        <v>6602</v>
+      </c>
+      <c r="B2693" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - VALORES FATURADOS</t>
+        </is>
+      </c>
+      <c r="C2693" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" t="n">
+        <v>6603</v>
+      </c>
+      <c r="B2694" t="inlineStr">
+        <is>
+          <t>COMPROVANTES COM FILIAL [BOLETOS] V2</t>
+        </is>
+      </c>
+      <c r="C2694" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" t="n">
+        <v>6604</v>
+      </c>
+      <c r="B2695" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - CONTAS PAGAS</t>
+        </is>
+      </c>
+      <c r="C2695" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" t="n">
+        <v>6605</v>
+      </c>
+      <c r="B2696" t="inlineStr">
+        <is>
+          <t>ECO CENTAURO - CONTAS PAGAS V2</t>
+        </is>
+      </c>
+      <c r="C2696" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B2697" t="inlineStr">
+        <is>
+          <t>SICOOB - 2445446-7</t>
+        </is>
+      </c>
+      <c r="C2697" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" t="n">
+        <v>6606</v>
+      </c>
+      <c r="B2698" t="inlineStr">
+        <is>
+          <t>SPDATA - MOVIMENTO POR CDC ANALITICO</t>
+        </is>
+      </c>
+      <c r="C2698" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" t="n">
+        <v>6607</v>
+      </c>
+      <c r="B2699" t="inlineStr">
+        <is>
+          <t>PUTRO ADP - RESUMO DA FOLHA</t>
+        </is>
+      </c>
+      <c r="C2699" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" t="n">
+        <v>6608</v>
+      </c>
+      <c r="B2700" t="inlineStr">
+        <is>
+          <t>DOMÍNIO - CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2700" t="inlineStr"/>
+    </row>
+    <row r="2701">
+      <c r="A2701" t="n">
+        <v>6609</v>
+      </c>
+      <c r="B2701" t="inlineStr">
+        <is>
+          <t>GESTOR - DOCUMENTOS BAIXADOS</t>
+        </is>
+      </c>
+      <c r="C2701" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" t="n">
+        <v>6610</v>
+      </c>
+      <c r="B2702" t="inlineStr">
+        <is>
+          <t>ITAU - FRANCESINHA V2</t>
+        </is>
+      </c>
+      <c r="C2702" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" t="n">
+        <v>6611</v>
+      </c>
+      <c r="B2703" t="inlineStr">
+        <is>
+          <t>GOVERNO FEDERAL - GRU</t>
+        </is>
+      </c>
+      <c r="C2703" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" t="n">
+        <v>6612</v>
+      </c>
+      <c r="B2704" t="inlineStr">
+        <is>
+          <t>EXODUS - RELATÓRIO DE VENDAS</t>
+        </is>
+      </c>
+      <c r="C2704" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" t="n">
+        <v>6613</v>
+      </c>
+      <c r="B2705" t="inlineStr">
+        <is>
+          <t>GES - ASDR</t>
+        </is>
+      </c>
+      <c r="C2705" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B2706" t="inlineStr">
+        <is>
+          <t>GES - DÉBITOS DOS CONVENIOS</t>
+        </is>
+      </c>
+      <c r="C2706" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" t="n">
+        <v>6615</v>
+      </c>
+      <c r="B2707" t="inlineStr">
+        <is>
+          <t>SGLOC - EXTRATO CONTA CORRENTE</t>
+        </is>
+      </c>
+      <c r="C2707" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" t="n">
+        <v>6616</v>
+      </c>
+      <c r="B2708" t="inlineStr">
+        <is>
+          <t>MEGA - EXTRATO BANCÁRIO ANALITICO</t>
+        </is>
+      </c>
+      <c r="C2708" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" t="n">
+        <v>6617</v>
+      </c>
+      <c r="B2709" t="inlineStr">
+        <is>
+          <t>GES - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2709" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" t="n">
+        <v>6618</v>
+      </c>
+      <c r="B2710" t="inlineStr">
+        <is>
+          <t>GES - CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2710" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" t="n">
+        <v>6619</v>
+      </c>
+      <c r="B2711" t="inlineStr">
+        <is>
+          <t>GES - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2711" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" t="n">
+        <v>6620</v>
+      </c>
+      <c r="B2712" t="inlineStr">
+        <is>
+          <t>3LM SOFTWARE - EXTRATO DE CONTA CORRENTE</t>
+        </is>
+      </c>
+      <c r="C2712" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" t="n">
+        <v>6621</v>
+      </c>
+      <c r="B2713" t="inlineStr">
+        <is>
+          <t>GES - DÉBITOS DOS CONTRIBUINTES</t>
+        </is>
+      </c>
+      <c r="C2713" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" t="n">
+        <v>6622</v>
+      </c>
+      <c r="B2714" t="inlineStr">
+        <is>
+          <t>UAU! SOFTWARE - CONTAS RECEBIDAS V2</t>
+        </is>
+      </c>
+      <c r="C2714" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" t="n">
+        <v>6623</v>
+      </c>
+      <c r="B2715" t="inlineStr">
+        <is>
+          <t>PET SHOP CONTROL - RELATÓRIO DE CONTAS</t>
+        </is>
+      </c>
+      <c r="C2715" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B2716" t="inlineStr">
+        <is>
+          <t>BB EXTRATO POR PERÍODO PDF (55561-4)</t>
+        </is>
+      </c>
+      <c r="C2716" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" t="n">
+        <v>6624</v>
+      </c>
+      <c r="B2717" t="inlineStr">
+        <is>
+          <t>CONTROLLE - RELATÓRIO PERSONALIZADO</t>
+        </is>
+      </c>
+      <c r="C2717" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" t="n">
+        <v>6625</v>
+      </c>
+      <c r="B2718" t="inlineStr">
+        <is>
+          <t>PET SHOP CONTROL - AUDITORIA DE VENDA</t>
+        </is>
+      </c>
+      <c r="C2718" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" t="n">
+        <v>6626</v>
+      </c>
+      <c r="B2719" t="inlineStr">
+        <is>
+          <t>MAGALUPAY - EXTRATO DA CARTEIRA</t>
+        </is>
+      </c>
+      <c r="C2719" t="inlineStr"/>
+    </row>
+    <row r="2720">
+      <c r="A2720" t="n">
+        <v>2317</v>
+      </c>
+      <c r="B2720" t="inlineStr">
+        <is>
+          <t>BLING - CONCILIAÇÃO NUBANK</t>
+        </is>
+      </c>
+      <c r="C2720" t="inlineStr"/>
+    </row>
+    <row r="2721">
+      <c r="A2721" t="n">
+        <v>6627</v>
+      </c>
+      <c r="B2721" t="inlineStr">
+        <is>
+          <t>GESTOR - NEGÓCIOS REALIZADOS</t>
+        </is>
+      </c>
+      <c r="C2721" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B2722" t="inlineStr">
+        <is>
+          <t>NUBANK - EXTRATO FILIAL</t>
+        </is>
+      </c>
+      <c r="C2722" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" t="n">
+        <v>6628</v>
+      </c>
+      <c r="B2723" t="inlineStr">
+        <is>
+          <t>GOWD - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2723" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" t="n">
+        <v>6629</v>
+      </c>
+      <c r="B2724" t="inlineStr">
+        <is>
+          <t>GERENTE MAX - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2724" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" t="n">
+        <v>6630</v>
+      </c>
+      <c r="B2725" t="inlineStr">
+        <is>
+          <t>SISVETOR -  DESPESAS REALIZADAS</t>
+        </is>
+      </c>
+      <c r="C2725" t="inlineStr"/>
+    </row>
+    <row r="2726">
+      <c r="A2726" t="n">
+        <v>6631</v>
+      </c>
+      <c r="B2726" t="inlineStr">
+        <is>
+          <t>TOTVS - FOLHA ANALITICA MENSAL</t>
+        </is>
+      </c>
+      <c r="C2726" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" t="n">
+        <v>6632</v>
+      </c>
+      <c r="B2727" t="inlineStr">
+        <is>
+          <t>IOB - RESUMO GPS</t>
+        </is>
+      </c>
+      <c r="C2727" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" t="n">
+        <v>6633</v>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>IFOOD - REPASSE</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" t="n">
+        <v>6634</v>
+      </c>
+      <c r="B2729" t="inlineStr">
+        <is>
+          <t>STRATEGIX - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2729" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" t="n">
+        <v>6635</v>
+      </c>
+      <c r="B2730" t="inlineStr">
+        <is>
+          <t>BB - RELAÇÃO DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2730" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" t="n">
+        <v>6636</v>
+      </c>
+      <c r="B2731" t="inlineStr">
+        <is>
+          <t>ASSAS - COMPROVANTE DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2731" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" t="n">
+        <v>6637</v>
+      </c>
+      <c r="B2732" t="inlineStr">
+        <is>
+          <t>REALCLUB - RECEBIMENTOS DO MÓDULO CAIXA</t>
+        </is>
+      </c>
+      <c r="C2732" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" t="n">
+        <v>6638</v>
+      </c>
+      <c r="B2733" t="inlineStr">
+        <is>
+          <t>SISPRIME - FATURA</t>
+        </is>
+      </c>
+      <c r="C2733" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" t="n">
+        <v>6639</v>
+      </c>
+      <c r="B2734" t="inlineStr">
+        <is>
+          <t>UP VENDAS - DEMONSTRATIVO DOS VALORES PAGOS PELO ESTABELECIMENTO</t>
+        </is>
+      </c>
+      <c r="C2734" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" t="n">
+        <v>6640</v>
+      </c>
+      <c r="B2735" t="inlineStr">
+        <is>
+          <t>VIASOFT CONSTRUSHOW - EXTRATO DO PORTADOR</t>
+        </is>
+      </c>
+      <c r="C2735" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" t="n">
+        <v>6641</v>
+      </c>
+      <c r="B2736" t="inlineStr">
+        <is>
+          <t>SANTANDER - BOLETOS</t>
+        </is>
+      </c>
+      <c r="C2736" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" t="n">
+        <v>6642</v>
+      </c>
+      <c r="B2737" t="inlineStr">
+        <is>
+          <t>BANCO DO BRASIL - BOLETOS</t>
+        </is>
+      </c>
+      <c r="C2737" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" t="n">
+        <v>6643</v>
+      </c>
+      <c r="B2738" t="inlineStr">
+        <is>
+          <t>UAIRANGO - RESUMO DE PEDIDOS APROVADOS</t>
+        </is>
+      </c>
+      <c r="C2738" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" t="n">
+        <v>6644</v>
+      </c>
+      <c r="B2739" t="inlineStr">
+        <is>
+          <t>SUPERLOGICA - MOVIMENTAÇÃO DAS CONTAS BANCÁRIAS</t>
+        </is>
+      </c>
+      <c r="C2739" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" t="n">
+        <v>6645</v>
+      </c>
+      <c r="B2740" t="inlineStr">
+        <is>
+          <t>MASTERMAQ SOFTWARE -  RELAÇÃO DE FATURAS EM ABERTO</t>
+        </is>
+      </c>
+      <c r="C2740" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" t="n">
+        <v>6646</v>
+      </c>
+      <c r="B2741" t="inlineStr">
+        <is>
+          <t>SI9 SISTEMAS - RELATÓRIO DE FECHAMENTO DE BANCO</t>
+        </is>
+      </c>
+      <c r="C2741" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" t="n">
+        <v>1336</v>
+      </c>
+      <c r="B2742" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 388650 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2742" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" t="n">
+        <v>1370</v>
+      </c>
+      <c r="B2743" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 389320- PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2743" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" t="n">
+        <v>1342</v>
+      </c>
+      <c r="B2744" t="inlineStr">
+        <is>
+          <t>BANCO ARBI - EXTRATO - C/C 387425 - PAYHOP</t>
+        </is>
+      </c>
+      <c r="C2744" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="n">
+        <v>6647</v>
+      </c>
+      <c r="B2745" t="inlineStr">
+        <is>
+          <t>EWR - RELATÓRIO DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2745" t="inlineStr"/>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="n">
+        <v>6648</v>
+      </c>
+      <c r="B2746" t="inlineStr">
+        <is>
+          <t>SYSCAR  - RELATÓRIO GESTÃO FINANCEIRA</t>
+        </is>
+      </c>
+      <c r="C2746" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="n">
+        <v>6649</v>
+      </c>
+      <c r="B2747" t="inlineStr">
+        <is>
+          <t>QUIVER - RELATÓRIO DE CONTAS PAGAS</t>
+        </is>
+      </c>
+      <c r="C2747" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B2748" t="inlineStr">
+        <is>
+          <t>BANESTES 870263 - 1</t>
+        </is>
+      </c>
+      <c r="C2748" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="n">
+        <v>6650</v>
+      </c>
+      <c r="B2749" t="inlineStr">
+        <is>
+          <t>SERVICE LOGIC - RECEBIMENTOS</t>
+        </is>
+      </c>
+      <c r="C2749" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="n">
+        <v>6651</v>
+      </c>
+      <c r="B2750" t="inlineStr">
+        <is>
+          <t>SERVICE LOGIC - CONTRATO TRANSPORTE</t>
+        </is>
+      </c>
+      <c r="C2750" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="n">
+        <v>6652</v>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>CONTA AZUL - FATURA DE LOCAÇÃO</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="n">
+        <v>6653</v>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>CONTAINER SOLUTION - RELATÓRIO DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr"/>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="n">
+        <v>6654</v>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>SPINCARE - TITULOS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="n">
+        <v>6655</v>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>ALPHA 7 - ANALISE DE NOTAS FISCAIS DE ENTRADA</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" t="n">
+        <v>6656</v>
+      </c>
+      <c r="B2755" t="inlineStr">
+        <is>
+          <t>SISTEMA BIAGRE - EXTRATO DE CONTAS</t>
+        </is>
+      </c>
+      <c r="C2755" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B2756" t="inlineStr">
+        <is>
+          <t>EXTRATO 914-0</t>
+        </is>
+      </c>
+      <c r="C2756" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" t="n">
+        <v>6657</v>
+      </c>
+      <c r="B2757" t="inlineStr">
+        <is>
+          <t>OBJETIVA - RELATÓRIO DE PAGAMENTO DE CLIENTES</t>
+        </is>
+      </c>
+      <c r="C2757" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" t="n">
+        <v>6658</v>
+      </c>
+      <c r="B2758" t="inlineStr">
+        <is>
+          <t>LH SISTEMAS E CONSULTORIA - RELATÓRIO DE CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2758" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" t="n">
+        <v>6659</v>
+      </c>
+      <c r="B2759" t="inlineStr">
+        <is>
+          <t>ULTRACAR - MOVIMENTO DE CAIXA</t>
+        </is>
+      </c>
+      <c r="C2759" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" t="n">
+        <v>6660</v>
+      </c>
+      <c r="B2760" t="inlineStr">
+        <is>
+          <t>TOTVS - RESUMO DA FOLHA V2</t>
+        </is>
+      </c>
+      <c r="C2760" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" t="n">
+        <v>6661</v>
+      </c>
+      <c r="B2761" t="inlineStr">
+        <is>
+          <t>NFE - XML DE ENTRADA</t>
+        </is>
+      </c>
+      <c r="C2761" t="inlineStr">
+        <is>
+          <t>XML</t>
+        </is>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" t="n">
+        <v>6662</v>
+      </c>
+      <c r="B2762" t="inlineStr">
+        <is>
+          <t>OBJETIVA - RELATÓRIO DE PAGAMENTO DE FORNECEDORES</t>
+        </is>
+      </c>
+      <c r="C2762" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" t="n">
+        <v>6663</v>
+      </c>
+      <c r="B2763" t="inlineStr">
+        <is>
+          <t>ZENITE GE - EXTRATO V2</t>
+        </is>
+      </c>
+      <c r="C2763" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" t="n">
+        <v>6664</v>
+      </c>
+      <c r="B2764" t="inlineStr">
+        <is>
+          <t>IXC SOFT - RELATÓRIO DA CONTA CAIXA SANGRIA</t>
+        </is>
+      </c>
+      <c r="C2764" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" t="n">
+        <v>6665</v>
+      </c>
+      <c r="B2765" t="inlineStr">
+        <is>
+          <t>COMMERCE SISTEMAS - CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2765" t="inlineStr"/>
+    </row>
+    <row r="2766">
+      <c r="A2766" t="n">
+        <v>6666</v>
+      </c>
+      <c r="B2766" t="inlineStr">
+        <is>
+          <t>AVEC - SALÃOVIP  - PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2766" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" t="n">
+        <v>6667</v>
+      </c>
+      <c r="B2767" t="inlineStr">
+        <is>
+          <t>COMMERCE SISTEMAS - CONTAS A RECEBER</t>
+        </is>
+      </c>
+      <c r="C2767" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" t="n">
+        <v>6668</v>
+      </c>
+      <c r="B2768" t="inlineStr">
+        <is>
+          <t>ALTERDATA - PROVISÃO DE 13º SALARIO</t>
+        </is>
+      </c>
+      <c r="C2768" t="inlineStr"/>
+    </row>
+    <row r="2769">
+      <c r="A2769" t="n">
+        <v>6669</v>
+      </c>
+      <c r="B2769" t="inlineStr">
+        <is>
+          <t>SEFAZ - EXTRATO DEMONSTRATIVO DA FATURA</t>
+        </is>
+      </c>
+      <c r="C2769" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" t="n">
+        <v>6670</v>
+      </c>
+      <c r="B2770" t="inlineStr">
+        <is>
+          <t>OBJETIVA - PAGAMENTOS DE FORNECEDOR</t>
+        </is>
+      </c>
+      <c r="C2770" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" t="n">
+        <v>6671</v>
+      </c>
+      <c r="B2771" t="inlineStr">
+        <is>
+          <t>SANKHYA - EXTRATO BANCARIO</t>
+        </is>
+      </c>
+      <c r="C2771" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" t="n">
+        <v>6672</v>
+      </c>
+      <c r="B2772" t="inlineStr">
+        <is>
+          <t>SAID - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2772" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" t="n">
+        <v>6673</v>
+      </c>
+      <c r="B2773" t="inlineStr">
+        <is>
+          <t>WVETRO - EXTRATO BANCÁRIO</t>
+        </is>
+      </c>
+      <c r="C2773" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" t="n">
+        <v>6674</v>
+      </c>
+      <c r="B2774" t="inlineStr">
+        <is>
+          <t>LIDERW - AVISO PRÉVIO DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="C2774" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" t="n">
+        <v>6675</v>
+      </c>
+      <c r="B2775" t="inlineStr">
+        <is>
+          <t>UNIMED - ANALITICO DE TAXA</t>
+        </is>
+      </c>
+      <c r="C2775" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" t="n">
+        <v>6676</v>
+      </c>
+      <c r="B2776" t="inlineStr">
+        <is>
+          <t>INNET SOLUÇÕES - DUPLICATAS POR DATA DE RECEBIMENTO</t>
+        </is>
+      </c>
+      <c r="C2776" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" t="n">
+        <v>6677</v>
+      </c>
+      <c r="B2777" t="inlineStr">
+        <is>
+          <t>ELO - FATURA DE CARTÃO</t>
+        </is>
+      </c>
+      <c r="C2777" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B2778" t="inlineStr">
+        <is>
+          <t>CONNECTERE - RELATÓRIO QI</t>
+        </is>
+      </c>
+      <c r="C2778" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" t="n">
+        <v>6678</v>
+      </c>
+      <c r="B2779" t="inlineStr">
+        <is>
+          <t>INNET SOLUÇÕES - DUPLICATAS POR DATA DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2779" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" t="n">
+        <v>1283</v>
+      </c>
+      <c r="B2780" t="inlineStr">
+        <is>
+          <t>PLANILHA DESPESAS BANCO SICRED - CLINICA CIRURGICA S.J.</t>
+        </is>
+      </c>
+      <c r="C2780" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" t="n">
+        <v>6679</v>
+      </c>
+      <c r="B2781" t="inlineStr">
+        <is>
+          <t>SGBR - LISTAGEM DE PAGAMENTOS</t>
+        </is>
+      </c>
+      <c r="C2781" t="inlineStr"/>
+    </row>
+    <row r="2782">
+      <c r="A2782" t="n">
+        <v>6680</v>
+      </c>
+      <c r="B2782" t="inlineStr">
+        <is>
+          <t>CONSISA - RESUMO DA FOLHA MENSAL - P/ FILIAL</t>
+        </is>
+      </c>
+      <c r="C2782" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" t="n">
+        <v>6681</v>
+      </c>
+      <c r="B2783" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - RECEBIMENTOS</t>
+        </is>
+      </c>
+      <c r="C2783" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" t="n">
+        <v>6682</v>
+      </c>
+      <c r="B2784" t="inlineStr">
+        <is>
+          <t>RK SOFTWARE - PAGAMENTOS NO PERIODO</t>
+        </is>
+      </c>
+      <c r="C2784" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" t="n">
+        <v>6683</v>
+      </c>
+      <c r="B2785" t="inlineStr">
+        <is>
+          <t>BB - INVESTIMENTOS CDB</t>
+        </is>
+      </c>
+      <c r="C2785" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2786">
+      <c r="A2786" t="n">
+        <v>6684</v>
+      </c>
+      <c r="B2786" t="inlineStr">
+        <is>
+          <t>BRASTEL - EXTRATO DAS CONTAS</t>
+        </is>
+      </c>
+      <c r="C2786" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" t="n">
+        <v>6685</v>
+      </c>
+      <c r="B2787" t="inlineStr">
+        <is>
+          <t>SIAGRI - CONTAS RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C2787" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" t="n">
+        <v>6686</v>
+      </c>
+      <c r="B2788" t="inlineStr">
+        <is>
+          <t>KAMINO - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2788" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" t="n">
+        <v>6687</v>
+      </c>
+      <c r="B2789" t="inlineStr">
+        <is>
+          <t>DESCONHECIDO - TITULOS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2789" t="inlineStr"/>
+    </row>
+    <row r="2790">
+      <c r="A2790" t="n">
+        <v>6688</v>
+      </c>
+      <c r="B2790" t="inlineStr">
+        <is>
+          <t>DOMÍNIO - RESUMO GERAL V2</t>
+        </is>
+      </c>
+      <c r="C2790" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B2791" t="inlineStr">
+        <is>
+          <t>KOINONIA SOFTWARE - RECEBIDAS</t>
+        </is>
+      </c>
+      <c r="C2791" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B2792" t="inlineStr">
+        <is>
+          <t>BANCO ABC - BIG MATRIZ 1288</t>
+        </is>
+      </c>
+      <c r="C2792" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" t="n">
+        <v>6690</v>
+      </c>
+      <c r="B2793" t="inlineStr">
+        <is>
+          <t>KOINONIA SOFTWARE - CONTAS PAGAS</t>
+        </is>
+      </c>
+      <c r="C2793" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" t="n">
+        <v>6691</v>
+      </c>
+      <c r="B2794" t="inlineStr">
+        <is>
+          <t>IDEALIZE SISTEMAS - EXTRATO BANCÁRIO</t>
+        </is>
+      </c>
+      <c r="C2794" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" t="n">
+        <v>6692</v>
+      </c>
+      <c r="B2795" t="inlineStr">
+        <is>
+          <t>SICOOB - EXTRATO DE OPERAÇÃO DE CRÉDITO</t>
+        </is>
+      </c>
+      <c r="C2795" t="inlineStr"/>
+    </row>
+    <row r="2796">
+      <c r="A2796" t="n">
+        <v>6693</v>
+      </c>
+      <c r="B2796" t="inlineStr">
+        <is>
+          <t>NEXT ERP - RELATÓRIO DE CONTAS A PAGAR</t>
+        </is>
+      </c>
+      <c r="C2796" t="inlineStr"/>
+    </row>
+    <row r="2797">
+      <c r="A2797" t="n">
+        <v>6694</v>
+      </c>
+      <c r="B2797" t="inlineStr">
+        <is>
+          <t>SANKHYA - RECIBO DE REPASSE</t>
+        </is>
+      </c>
+      <c r="C2797" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" t="n">
+        <v>6695</v>
+      </c>
+      <c r="B2798" t="inlineStr">
+        <is>
+          <t>VAREJO FACIL - CONTAS A PAGAR ANALITICO V2</t>
+        </is>
+      </c>
+      <c r="C2798" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" t="n">
+        <v>6696</v>
+      </c>
+      <c r="B2799" t="inlineStr">
+        <is>
+          <t>DP SISTEMA - TITULOS PAGOS</t>
+        </is>
+      </c>
+      <c r="C2799" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" t="n">
+        <v>6697</v>
+      </c>
+      <c r="B2800" t="inlineStr">
+        <is>
+          <t>LOCAWEB - FATURA</t>
+        </is>
+      </c>
+      <c r="C2800" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" t="n">
+        <v>6698</v>
+      </c>
+      <c r="B2801" t="inlineStr">
+        <is>
+          <t>ETECH - DEMOSNTRATIVO DE DESPESAS</t>
+        </is>
+      </c>
+      <c r="C2801" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" t="n">
+        <v>6699</v>
+      </c>
+      <c r="B2802" t="inlineStr">
+        <is>
+          <t>BRB - FATURA</t>
+        </is>
+      </c>
+      <c r="C2802" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" t="n">
+        <v>6700</v>
+      </c>
+      <c r="B2803" t="inlineStr">
+        <is>
+          <t>AERO- DEMONSTRATIVO DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2803" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" t="n">
+        <v>6701</v>
+      </c>
+      <c r="B2804" t="inlineStr">
+        <is>
+          <t>ADIPLAN - RECIBO DE REPASSE</t>
+        </is>
+      </c>
+      <c r="C2804" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" t="n">
+        <v>6702</v>
+      </c>
+      <c r="B2805" t="inlineStr">
+        <is>
+          <t>HYPERLOCAL BANK - EXTRATO DA CONTA</t>
+        </is>
+      </c>
+      <c r="C2805" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" t="n">
+        <v>6703</v>
+      </c>
+      <c r="B2806" t="inlineStr">
+        <is>
+          <t>RECARGA PAY - EXTRATO</t>
+        </is>
+      </c>
+      <c r="C2806" t="inlineStr"/>
+    </row>
+    <row r="2807">
+      <c r="A2807" t="n">
+        <v>6704</v>
+      </c>
+      <c r="B2807" t="inlineStr">
+        <is>
+          <t>LIDERW - FOLHA DE PAGAMENTO</t>
+        </is>
+      </c>
+      <c r="C2807" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B2808" t="inlineStr">
+        <is>
+          <t>EXTRATO BANCO DO BRASIL - DULCIMAR</t>
+        </is>
+      </c>
+      <c r="C2808" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
